--- a/Test Results/Excel/Load_Testing_Performance_Report.xlsx
+++ b/Test Results/Excel/Load_Testing_Performance_Report.xlsx
@@ -484,7 +484,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>POST /api/auth/login Baseline Load Test</t>
+          <t>User Auth Login Baseline Load Test (100 VUs)</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>POST /api/auth/login Stress Test (200 VUs)</t>
+          <t>High Concurrency Auth Login Stress (200 VUs)</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -564,7 +564,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>POST /api/auth/login Stress Test (500 VUs)</t>
+          <t>Extreme User Auth Login Saturation (500 VUs)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -604,7 +604,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>POST /api/auth/login Peak Burst (1000 VUs)</t>
+          <t>Peak Burst Auth Login Spike Test (1000 VUs)</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -644,7 +644,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>POST /api/auth/login Invalid Password Flood (300 VUs)</t>
+          <t>Invalid Password Flood Attempt (300 VUs)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -684,7 +684,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>POST /api/auth/login SQLi Payload Injection Load</t>
+          <t>SQL Injection Security Payload Load Test</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -724,7 +724,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>POST /api/auth/login XSS Payload Injection Load</t>
+          <t>XSS Injection Security Payload Load Test</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -764,7 +764,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>POST /api/auth/login MFA Token Verification Spike</t>
+          <t>MFA Verification Code Validation Spike</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -804,7 +804,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>POST /api/auth/login Expired Token Refresh Flood</t>
+          <t>Expired Auth Token Refresh Request Flood</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -844,7 +844,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>POST /api/auth/login Password Reset Request Burst</t>
+          <t>Password Recovery Verification Email Burst</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -884,7 +884,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>POST /api/auth/login OAuth2 Google Callback Concurrency</t>
+          <t>Google OAuth2 SSO Callback Redirection Load</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -924,7 +924,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>POST /api/auth/login OAuth2 GitHub Callback Concurrency</t>
+          <t>GitHub OAuth2 SSO Callback Authorization Load</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -964,7 +964,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>POST /api/auth/login Concurrent Rate Limiter Check</t>
+          <t>Concurrent API Rate Limiter Verification</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1004,7 +1004,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>POST /api/auth/login Malformed JSON Payload Stress</t>
+          <t>Malformed JSON Auth Request Body Stress</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1044,7 +1044,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>POST /api/auth/login Zero-Length Payload Flood</t>
+          <t>Zero-Length Payload Rejection Throughput</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1084,7 +1084,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>POST /api/auth/login Large Payload Stress (1MB JSON)</t>
+          <t>Overly Large 1MB JSON Payload Stress</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1124,7 +1124,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>POST /api/auth/login Session Cookie Serialization Load</t>
+          <t>Session Cookie Serialization Latency Test</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1164,7 +1164,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>POST /api/auth/login JWT Signing Key Rotation Load</t>
+          <t>JWT Signing Key Rotation Pass-Through</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1204,7 +1204,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>POST /api/auth/login Argon2 Hashing CPU Saturation</t>
+          <t>Argon2 Password Hashing CPU Saturation</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1244,7 +1244,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>POST /api/auth/login Bcrypt Work Factor 12 Load</t>
+          <t>Bcrypt Work Factor 12 Hashing CPU Benchmark</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1284,7 +1284,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>POST /api/auth/login Simultaneous IP Subnet Flood</t>
+          <t>Simultaneous IP Subnet Traffic Flood</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1324,7 +1324,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>POST /api/auth/login User Lockout Database Write Load</t>
+          <t>User Account Lockout DB Write Load</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1364,7 +1364,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>POST /api/auth/login CORS Preflight OPTIONS Flood</t>
+          <t>CORS Preflight OPTIONS Requests Burst</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1404,7 +1404,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>POST /api/auth/login TLS Handshake Connection Burst</t>
+          <t>TLS 1.3 Handshake Connection Throughput</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1444,7 +1444,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>POST /api/auth/login Endurance Run (100 VUs for 10m)</t>
+          <t>Sustained 10-Minute Auth Endurance Run</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1484,7 +1484,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Baseline Landmark Processing (100 VUs)</t>
+          <t>Live Pose Landmark Ingestion (100 VUs)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1524,7 +1524,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>POST /api/live-frame High Frequency Ingestion (500 VUs)</t>
+          <t>High Frequency Telemetry Ingestion (500 VUs)</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1564,7 +1564,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>POST /api/live-frame MediaPipe 33 Landmark Payload Load</t>
+          <t>MediaPipe 33 Landmark Payload Benchmark</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1604,7 +1604,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Real-Time Slouch Angle Calc Benchmark</t>
+          <t>Real-Time Slouch Calculation Throughput</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1644,7 +1644,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Concurrent Session Telemetry Isolation</t>
+          <t>Concurrent User Session Telemetry Isolation</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1684,7 +1684,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Missing Visibility Score Boundary Test</t>
+          <t>Missing Visibility Score Boundary Rejection</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1724,7 +1724,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Out-of-Order Timestamp Sequence Load</t>
+          <t>Out-of-Order Timestamp Frame Sequence Test</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1764,7 +1764,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>POST /api/live-frame High Noise Landmark Coordinate Jitter</t>
+          <t>High Noise Coordinate Jitter Handling</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1804,7 +1804,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Batch Frame Payload (10 frames/pkt)</t>
+          <t>Batch Frame Telemetry Packet (10 frames/pkt)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1844,7 +1844,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>POST /api/live-frame WebSocket Fallback HTTP Long Polling</t>
+          <t>WebSocket Fallback HTTP Long Polling Test</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1884,7 +1884,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>POST /api/live-frame GPU Acceleration Pipeline Pass-Through</t>
+          <t>GPU Accelerated Processing Pass-Through</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1924,7 +1924,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>POST /api/live-frame CPU-bound Math Calculation Stress</t>
+          <t>Math Calculation Intensive CPU Stress</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1964,7 +1964,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Memory Leak Inspection (20m continuous)</t>
+          <t>Continuous 20-Minute Telemetry Memory Inspection</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2004,7 +2004,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Incomplete Landmark Array Payload</t>
+          <t>Incomplete Landmark Array Rejection Test</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -2044,7 +2044,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Negative Angle Value Edge Case Load</t>
+          <t>Negative Coordinate Value Edge Case Handling</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2084,7 +2084,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Double Precision Floating Point Coordinates</t>
+          <t>Double Precision Float Landmark Processing</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -2124,7 +2124,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Concurrent Alert Trigger Computation</t>
+          <t>Concurrent Slouch Alert Trigger Processing</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2164,7 +2164,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Multi-User Stream Parallel Processing</t>
+          <t>Multi-User Video Stream Parallel Pipeline</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2204,7 +2204,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Live Posture Score Moving Average Cache</t>
+          <t>Moving Average Posture Score Caching Test</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2244,7 +2244,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Gzip Compressed Telemetry Request Body</t>
+          <t>Gzip Compressed Telemetry Ingestion</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2284,7 +2284,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Brotli Compressed Telemetry Request Body</t>
+          <t>Brotli Compressed Telemetry Ingestion</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2324,7 +2324,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Peak Burst Saturation (1200 VUs)</t>
+          <t>Peak Telemetry Burst Saturation (1200 VUs)</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -2364,7 +2364,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Database Buffer Queue Overflow Test</t>
+          <t>Database Buffer Queue Overflow Resiliency</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2404,7 +2404,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Redis Pub/Sub Stream Latency Check</t>
+          <t>Redis Pub/Sub Stream Telemetry Latency</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -2444,7 +2444,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Kafka Ingestion Pipeline Stress</t>
+          <t>Kafka Telemetry Message Ingestion Pipeline</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2484,7 +2484,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>POST /api/live-frame RabbitMQ Telemetry Message Queue Load</t>
+          <t>RabbitMQ Message Broker Backpressure Test</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -2524,7 +2524,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Zero Landmark Detection Frame Handling</t>
+          <t>Zero Landmark Frame Fast Discard Speed</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2564,7 +2564,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Sudden FPS Drop (60 -&gt; 5 FPS) Resiliency</t>
+          <t>Sudden FPS Drop Stream Recovery Test</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -2604,7 +2604,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>POST /api/live-frame 3D Spatial Z-Axis Landmark Processing</t>
+          <t>3D Spatial Z-Axis Landmark Processing</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2644,7 +2644,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>POST /api/live-frame Posture Session Auto-Finalization Load</t>
+          <t>Automatic Session Finalization Cleanup</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -2684,7 +2684,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>POST /api/upload-video 10MB MP4 Upload Baseline (50 VUs)</t>
+          <t>10MB MP4 Media Upload Baseline (50 VUs)</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2724,7 +2724,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>POST /api/upload-video 50MB MP4 Upload Stress (100 VUs)</t>
+          <t>50MB MP4 Media Upload Stress (100 VUs)</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -2764,7 +2764,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>POST /api/upload-video 100MB Large File Upload Saturation</t>
+          <t>100MB Large Video Upload Saturation</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2804,7 +2804,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>POST /api/upload-video Multipart Form Data Streaming Throughput</t>
+          <t>Multipart Form Data Streaming Throughput</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -2844,7 +2844,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>POST /api/upload-video Cloudinary API Presigned Upload Burst</t>
+          <t>Cloudinary API Presigned Upload Burst</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2884,7 +2884,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>POST /api/upload-video FFmpeg Server Transcoding Concurrency</t>
+          <t>FFmpeg Transcoding Server Concurrency</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -2924,7 +2924,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>POST /api/upload-video Corrupted Media Bitstream Rejection Load</t>
+          <t>Corrupted Video Bitstream Rejection Speed</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2964,7 +2964,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>POST /api/upload-video Concurrent Chunked Video Upload (5MB chunks)</t>
+          <t>Chunked Video Upload Parallelism (5MB Chunks)</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -3004,7 +3004,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>POST /api/upload-video Resume Interrupted Chunked Upload Load</t>
+          <t>Interrupted Upload Resumption Load Test</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3044,7 +3044,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>POST /api/upload-video Simultaneous WebM and MOV Format Upload</t>
+          <t>Simultaneous WebM and MOV Format Uploads</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -3084,7 +3084,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>POST /api/upload-video Disk I/O Write Saturation Benchmark</t>
+          <t>Disk Write I/O Saturation Throughput</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3124,7 +3124,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>POST /api/upload-video S3 Storage Bucket Upload Parallelism</t>
+          <t>AWS S3 Multi-Part Bucket Parallel Uploads</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -3164,7 +3164,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>POST /api/upload-video Media Keyframe Extraction CPU Burst</t>
+          <t>Keyframe Extraction CPU Utilization Burst</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3204,7 +3204,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>POST /api/upload-video Video Posture Score Generation Pipeline</t>
+          <t>AI Posture Score Generation Pipeline Speed</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -3244,7 +3244,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>POST /api/upload-video Temporary Storage Swap Space Cleaning</t>
+          <t>Temporary Storage Swap Space Purge Rate</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3284,7 +3284,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>POST /api/upload-video High Network Latency Simulation (300ms RTT)</t>
+          <t>High Network Latency Video Upload (300ms RTT)</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -3324,7 +3324,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>POST /api/upload-video Zero Byte Video Upload Rejection Speed</t>
+          <t>Zero Byte Video File Rejection Latency</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3364,7 +3364,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>POST /api/upload-video Virus Scanner Security Middleware Overhead</t>
+          <t>Antivirus Malware Scanning Overhead</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -3404,7 +3404,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>POST /api/upload-video Rate Limit Exceeded Upload Denial (HTTP 429)</t>
+          <t>Rate Limit Exceeded Denial (HTTP 429)</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3444,7 +3444,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>POST /api/upload-video Simultaneous Audio Stripping Pipeline</t>
+          <t>Simultaneous Audio Stripping Pipeline Load</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -3484,7 +3484,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>POST /api/upload-video Multi-resolution HLS Video Hashing</t>
+          <t>Multi-Bitrate HLS Video Encoding Latency</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3524,7 +3524,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>POST /api/upload-video Posture Thumbnail Image Generation Load</t>
+          <t>Posture Thumbnail Generation Queue Load</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -3564,7 +3564,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>POST /api/upload-video Parallel Video Posture AI Comparison</t>
+          <t>Parallel Dual-Video Posture Comparison</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3604,7 +3604,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>POST /api/upload-video CORS Upload Progress Event Listener Stress</t>
+          <t>CORS Upload Event Progress Dispatcher</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -3644,7 +3644,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>POST /api/upload-video Network Abort &amp; Connection Timeout Recovery</t>
+          <t>Network Drop Mid-Upload Connection Recovery</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -3684,7 +3684,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>GET /health Endpoint High-Frequency Polling (1000 VUs)</t>
+          <t>Health Endpoint High Frequency Polling (1000 VUs)</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -3724,7 +3724,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status Baseline Load (300 VUs)</t>
+          <t>System Status Monitoring Baseline (300 VUs)</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -3764,7 +3764,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status Heavy Stress (800 VUs)</t>
+          <t>System Status Monitoring Stress (800 VUs)</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -3804,7 +3804,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status Redis Cache Hit Ratio Validation</t>
+          <t>Redis In-Memory Cache Hit Ratio Benchmark</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -3844,7 +3844,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status Cache Miss Backend Query Pass-Through</t>
+          <t>Cache Miss Database Query Pass-Through</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -3884,7 +3884,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status Gunicorn Async Worker Loop Throughput</t>
+          <t>Gunicorn Async Worker Event Loop Throughput</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -3924,7 +3924,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status Load Balancer Round-Robin Check</t>
+          <t>Nginx Load Balancer Round-Robin Balancing</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -3964,7 +3964,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status Nginx Reverse Proxy Cache Benchmark</t>
+          <t>Nginx Reverse Proxy Static Cache Throughput</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4004,7 +4004,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status HTTP 304 Not Modified ETag Validation</t>
+          <t>HTTP 304 Not Modified Cache Validation</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -4044,7 +4044,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status CPU Usage Metrics Subsystem Load</t>
+          <t>CPU Utilization Subsystem Metric Endpoint</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4084,7 +4084,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status Memory Footprint Subsystem Query</t>
+          <t>RAM Footprint Subsystem Metric Endpoint</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -4124,7 +4124,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status Database Health Ping Concurrency</t>
+          <t>Database Health Ping Connectivity Check</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4164,7 +4164,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status Cloudinary SDK Connectivity Check</t>
+          <t>Cloudinary SDK Service Availability Check</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -4204,7 +4204,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status System Uptime Ticker Endpoint Load</t>
+          <t>System Uptime Ticker Metric Endpoint</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4244,7 +4244,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status Active Session Count Metrics Ingestion</t>
+          <t>Active Session Counter Ingestion Speed</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -4284,7 +4284,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status Unauthenticated Status Access Rate</t>
+          <t>Unauthenticated Public Monitoring Access</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4324,7 +4324,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status HTTP Keep-Alive Connection Reuse</t>
+          <t>HTTP Keep-Alive Persistent Socket Check</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -4364,7 +4364,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status Edge CDN Node Response Latency</t>
+          <t>Edge CDN Network Response Latency Test</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4404,7 +4404,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status Cloudflare DDoS Shield Simulation</t>
+          <t>Cloudflare DDoS Mitigation Shield Burst</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -4444,7 +4444,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status Backend Microservice Readiness Probe</t>
+          <t>Backend Microservice Readiness Probe Check</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4484,7 +4484,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status Kubernetes Liveness Probe Saturation</t>
+          <t>Kubernetes Liveness Probe Saturation Test</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -4524,7 +4524,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status High Latency Upstream Dependency Test</t>
+          <t>Upstream Service Dependency Timeout Check</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -4564,7 +4564,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status Maintenance Mode Flag Toggle Speed</t>
+          <t>System Maintenance Flag Instant Toggle</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -4604,7 +4604,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status Zero Payload Response Serialization</t>
+          <t>Empty Response Body Latency Benchmark</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -4644,7 +4644,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>GET /api/monitoring/status SSL Session ID Resumption Throughput</t>
+          <t>SSL Session ID Resumption Handshake Test</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -4684,7 +4684,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GET /api/session/history Paginated Query Baseline (100 VUs)</t>
+          <t>Paginated Session History Query Baseline</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -4724,7 +4724,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GET /api/session/history Indexed Range Scan Query (300 VUs)</t>
+          <t>Indexed Range Scan Query Stress (300 VUs)</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -4764,7 +4764,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GET /api/session/history Unindexed Search Query Stress (200 VUs)</t>
+          <t>Unindexed Full Text Search Query Load</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -4804,7 +4804,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>GET /api/session/history MongoDB Compound Index Lookup Load</t>
+          <t>MongoDB Compound Index Lookup Speed</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -4844,7 +4844,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>GET /api/session/history Complex Date Range Filter Aggregation</t>
+          <t>Complex Date Range Aggregation Pipeline</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -4884,7 +4884,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GET /api/session/history High Page Size (100 rows per page) Stress</t>
+          <t>High Page Size (100 Rows/Page) Fetch Stress</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -4924,7 +4924,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GET /api/session/history Sort by Posture Score Descending Load</t>
+          <t>Sort by Posture Score Descending Benchmark</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -4964,7 +4964,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>GET /api/session/history Sort by Duration Ascending Query Load</t>
+          <t>Sort by Duration Ascending Benchmark</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -5004,7 +5004,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>GET /api/session/history Full Text Search Filter Keyword Load</t>
+          <t>Full-Text Search Keyword Match Throughput</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -5044,7 +5044,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>GET /api/session/history Multi-tenant Account Isolation Query Check</t>
+          <t>Multi-Tenant Account Isolation Query Check</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -5084,7 +5084,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>GET /api/session/history Empty Result Set Query Response Speed</t>
+          <t>Empty Query Result Set Response Latency</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -5124,7 +5124,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>GET /api/session/history Database Connection Pool Starvation Test</t>
+          <t>Database Connection Pool Starvation Test</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -5164,7 +5164,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>GET /api/session/history Read Replica Database Load Balancing</t>
+          <t>Read Replica DB Query Load Balancing</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -5204,7 +5204,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>GET /api/session/history Redis Session Summary Cache Warm-up</t>
+          <t>Redis Session Summary Cache Warm-Up Speed</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -5244,7 +5244,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>GET /api/session/history Concurrent Session Deletion Conflict Test</t>
+          <t>Concurrent Session Deletion Write Load</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -5284,7 +5284,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GET /api/session/history Deep Pagination Page 500 Slow Query</t>
+          <t>Deep Pagination Page 500 Slow Query Test</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -5324,7 +5324,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GET /api/session/history JSON BSON Document Deserialization Benchmark</t>
+          <t>BSON Document Deserialization Performance</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -5364,7 +5364,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GET /api/session/history Large Session Note Text Blob Retrieval</t>
+          <t>Large Text Blob Session Note Fetch Speed</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -5404,7 +5404,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GET /api/session/history CORS Header Response overhead on GET</t>
+          <t>CORS Response Header Generation Load</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -5444,7 +5444,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GET /api/session/history JWT Verification Filter Latency Impact</t>
+          <t>JWT Authorization Middleware Overhead</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -5484,7 +5484,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GET /api/session/history Invalid Page Parameter Input Handling</t>
+          <t>Invalid Page Number Parameter Sanitization</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -5524,7 +5524,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GET /api/session/history Negative Limit Parameter Input Handling</t>
+          <t>Negative Limit Parameter Sanitization</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -5564,7 +5564,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GET /api/session/history SQL Join Overhead Benchmark (Relational DB)</t>
+          <t>Relational DB SQL Join Latency Benchmark</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -5604,7 +5604,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GET /api/session/history MongoDB Sharded Cluster Query Routing</t>
+          <t>MongoDB Sharded Cluster Query Router Load</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -5644,7 +5644,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>GET /api/session/history Gzip Response Compression Ratio Load</t>
+          <t>Gzip Response Stream Compression Throughput</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -5684,7 +5684,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Gunicorn Worker Saturation Test (4 Sync Workers)</t>
+          <t>Gunicorn Sync Worker Pool Saturation (4 Workers)</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -5724,7 +5724,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Gunicorn Gevent Async Worker Saturation Test (1000 Greenlets)</t>
+          <t>Gunicorn Gevent Async Greenlet Saturation (1000 VUs)</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -5764,7 +5764,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Uvicorn ASGI Engine Concurrency Benchmark</t>
+          <t>Uvicorn ASGI High Throughput Benchmark</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -5804,7 +5804,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Nginx Connection Pool Capacity Test (10,000 Worker Connections)</t>
+          <t>Nginx Worker Connection Pool Capacity (10k Conns)</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -5844,7 +5844,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Redis In-Memory Session Storage Throughput (50,000 Keys)</t>
+          <t>Redis In-Memory Store IOPS Benchmark (50k Keys)</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -5884,7 +5884,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MongoDB Primary Node Failover Resilience Test</t>
+          <t>MongoDB Primary Replica Failover Endurance</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -5924,7 +5924,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>RabbitMQ Message Broker Backpressure Under 10,000 msg/sec</t>
+          <t>RabbitMQ Message Queue Backpressure Test (10k msg/s)</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -5964,7 +5964,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Kafka Topic Partition Balance Under 100 Consumer Groups</t>
+          <t>Kafka Topic Partition Group Partitioning Load</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -6004,7 +6004,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Celery Distributed Task Queue Worker Saturation</t>
+          <t>Celery Background Task Queue Worker Load</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -6044,7 +6044,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PostgreSQL Connection Pooler (PgBouncer) Max Connections</t>
+          <t>PgBouncer PostgreSQL Connection Pool Limit</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -6084,7 +6084,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Docker Container CPU Quotas Throttling Test (2 vCPUs)</t>
+          <t>Docker Container 2 vCPU Quotas Throttling</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -6124,7 +6124,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Docker Container RAM Limit (512MB) Out-Of-Memory Test</t>
+          <t>Docker Container 512MB RAM Out-Of-Memory Test</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -6164,7 +6164,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Kubernetes Horizontal Pod Autoscaler (HPA) Scale-Up Time</t>
+          <t>Kubernetes Pod Autoscaler Scale-Up Latency</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -6204,7 +6204,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>AWS ALB (Application Load Balancer) Spike Ingestion</t>
+          <t>AWS Application Load Balancer Ingress Burst</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -6244,7 +6244,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Cloudflare Edge Network Cache Hit Efficiency</t>
+          <t>Cloudflare Global Edge Cache Hit Rate Benchmark</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -6284,7 +6284,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>AWS S3 File Download Bandwidth Saturation (1Gbps)</t>
+          <t>AWS S3 File Download 1Gbps Bandwidth Cap</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -6324,7 +6324,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Google Cloud Storage Multi-Region Bucket Read Load</t>
+          <t>Google Cloud Storage Multi-Region Bucket Read</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -6364,7 +6364,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Azure Blob Storage Concurrent SAS Token Access</t>
+          <t>Azure Blob SAS Security Token Access Throughput</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -6404,7 +6404,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Cloudinary Image Transformation Dynamic Caching Load</t>
+          <t>Cloudinary Dynamic Image Resizing Load</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -6444,7 +6444,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FastAPI Async Endpoint Event Loop Throughput</t>
+          <t>FastAPI Event Loop Non-Blocking Async IOPS</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -6484,7 +6484,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #021 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #021 Performance Benchmark</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -6524,7 +6524,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #022 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #022 Performance Benchmark</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -6564,7 +6564,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #023 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #023 Performance Benchmark</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -6604,7 +6604,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #024 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #024 Performance Benchmark</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -6644,7 +6644,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #025 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #025 Performance Benchmark</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -6684,7 +6684,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #026 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #026 Performance Benchmark</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -6724,7 +6724,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #027 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #027 Performance Benchmark</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -6764,7 +6764,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #028 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #028 Performance Benchmark</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -6804,7 +6804,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #029 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #029 Performance Benchmark</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -6844,7 +6844,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #030 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #030 Performance Benchmark</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -6884,7 +6884,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #031 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #031 Performance Benchmark</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -6924,7 +6924,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #032 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #032 Performance Benchmark</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -6964,7 +6964,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #033 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #033 Performance Benchmark</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -7004,7 +7004,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #034 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #034 Performance Benchmark</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -7044,7 +7044,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #035 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #035 Performance Benchmark</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -7084,7 +7084,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #036 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #036 Performance Benchmark</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -7124,7 +7124,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #037 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #037 Performance Benchmark</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -7164,7 +7164,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #038 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #038 Performance Benchmark</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -7204,7 +7204,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #039 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #039 Performance Benchmark</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -7244,7 +7244,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #040 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #040 Performance Benchmark</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -7284,7 +7284,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #041 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #041 Performance Benchmark</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -7324,7 +7324,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #042 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #042 Performance Benchmark</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -7364,7 +7364,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #043 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #043 Performance Benchmark</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -7404,7 +7404,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #044 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #044 Performance Benchmark</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -7444,7 +7444,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #045 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #045 Performance Benchmark</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -7484,7 +7484,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #046 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #046 Performance Benchmark</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -7524,7 +7524,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #047 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #047 Performance Benchmark</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -7564,7 +7564,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #048 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #048 Performance Benchmark</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -7604,7 +7604,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #049 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #049 Performance Benchmark</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -7644,7 +7644,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #050 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #050 Performance Benchmark</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -7684,7 +7684,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #051 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #051 Performance Benchmark</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -7724,7 +7724,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #052 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #052 Performance Benchmark</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -7764,7 +7764,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #053 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #053 Performance Benchmark</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -7804,7 +7804,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #054 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #054 Performance Benchmark</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -7844,7 +7844,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #055 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #055 Performance Benchmark</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -7884,7 +7884,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #056 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #056 Performance Benchmark</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -7924,7 +7924,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #057 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #057 Performance Benchmark</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -7964,7 +7964,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #058 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #058 Performance Benchmark</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -8004,7 +8004,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #059 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #059 Performance Benchmark</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -8044,7 +8044,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #060 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #060 Performance Benchmark</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -8084,7 +8084,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #061 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #061 Performance Benchmark</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -8124,7 +8124,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #062 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #062 Performance Benchmark</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -8164,7 +8164,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #063 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #063 Performance Benchmark</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -8204,7 +8204,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #064 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #064 Performance Benchmark</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -8244,7 +8244,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #065 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #065 Performance Benchmark</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -8284,7 +8284,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #066 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #066 Performance Benchmark</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -8324,7 +8324,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #067 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #067 Performance Benchmark</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -8364,7 +8364,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #068 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #068 Performance Benchmark</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -8404,7 +8404,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #069 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #069 Performance Benchmark</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -8444,7 +8444,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #070 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #070 Performance Benchmark</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -8484,7 +8484,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #071 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #071 Performance Benchmark</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -8524,7 +8524,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #072 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #072 Performance Benchmark</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -8564,7 +8564,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #073 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #073 Performance Benchmark</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -8604,7 +8604,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #074 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #074 Performance Benchmark</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -8644,7 +8644,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #075 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #075 Performance Benchmark</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -8684,7 +8684,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #076 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #076 Performance Benchmark</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -8724,7 +8724,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #077 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #077 Performance Benchmark</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -8764,7 +8764,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #078 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #078 Performance Benchmark</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -8804,7 +8804,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #079 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #079 Performance Benchmark</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -8844,7 +8844,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #080 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #080 Performance Benchmark</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -8884,7 +8884,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #081 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #081 Performance Benchmark</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -8924,7 +8924,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #082 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #082 Performance Benchmark</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -8964,7 +8964,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #083 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #083 Performance Benchmark</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -9004,7 +9004,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #084 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #084 Performance Benchmark</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -9044,7 +9044,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #085 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #085 Performance Benchmark</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -9084,7 +9084,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #086 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #086 Performance Benchmark</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -9124,7 +9124,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #087 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #087 Performance Benchmark</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -9164,7 +9164,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #088 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #088 Performance Benchmark</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -9204,7 +9204,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #089 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #089 Performance Benchmark</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -9244,7 +9244,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #090 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #090 Performance Benchmark</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -9284,7 +9284,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #091 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #091 Performance Benchmark</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -9324,7 +9324,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #092 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #092 Performance Benchmark</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -9364,7 +9364,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #093 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #093 Performance Benchmark</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -9404,7 +9404,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #094 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #094 Performance Benchmark</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -9444,7 +9444,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #095 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #095 Performance Benchmark</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -9484,7 +9484,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #096 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #096 Performance Benchmark</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -9524,7 +9524,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #097 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #097 Performance Benchmark</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -9564,7 +9564,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #098 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #098 Performance Benchmark</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -9604,7 +9604,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #099 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #099 Performance Benchmark</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -9644,7 +9644,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #100 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #100 Performance Benchmark</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -9684,7 +9684,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #101 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #101 Performance Benchmark</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -9724,7 +9724,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #102 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #102 Performance Benchmark</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -9764,7 +9764,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #103 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #103 Performance Benchmark</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -9804,7 +9804,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #104 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #104 Performance Benchmark</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -9844,7 +9844,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #105 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #105 Performance Benchmark</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -9884,7 +9884,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #106 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #106 Performance Benchmark</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -9924,7 +9924,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #107 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #107 Performance Benchmark</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -9964,7 +9964,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #108 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #108 Performance Benchmark</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -10004,7 +10004,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #109 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #109 Performance Benchmark</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -10044,7 +10044,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #110 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #110 Performance Benchmark</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -10084,7 +10084,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #111 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #111 Performance Benchmark</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -10124,7 +10124,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #112 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #112 Performance Benchmark</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -10164,7 +10164,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #113 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #113 Performance Benchmark</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -10204,7 +10204,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #114 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #114 Performance Benchmark</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -10244,7 +10244,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #115 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #115 Performance Benchmark</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -10284,7 +10284,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #116 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #116 Performance Benchmark</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -10324,7 +10324,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #117 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #117 Performance Benchmark</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -10364,7 +10364,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #118 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #118 Performance Benchmark</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -10404,7 +10404,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #119 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #119 Performance Benchmark</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -10444,7 +10444,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #120 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #120 Performance Benchmark</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -10484,7 +10484,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #121 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #121 Performance Benchmark</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -10524,7 +10524,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #122 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #122 Performance Benchmark</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -10564,7 +10564,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #123 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #123 Performance Benchmark</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -10604,7 +10604,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #124 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #124 Performance Benchmark</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -10644,7 +10644,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #125 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #125 Performance Benchmark</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -10684,7 +10684,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #126 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #126 Performance Benchmark</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -10724,7 +10724,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #127 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #127 Performance Benchmark</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -10764,7 +10764,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #128 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #128 Performance Benchmark</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -10804,7 +10804,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #129 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #129 Performance Benchmark</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -10844,7 +10844,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #130 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #130 Performance Benchmark</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -10884,7 +10884,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #131 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #131 Performance Benchmark</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -10924,7 +10924,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #132 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #132 Performance Benchmark</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -10964,7 +10964,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #133 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #133 Performance Benchmark</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -11004,7 +11004,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #134 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #134 Performance Benchmark</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -11044,7 +11044,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #135 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #135 Performance Benchmark</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -11084,7 +11084,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #136 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #136 Performance Benchmark</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -11124,7 +11124,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #137 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #137 Performance Benchmark</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -11164,7 +11164,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #138 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #138 Performance Benchmark</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -11204,7 +11204,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #139 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #139 Performance Benchmark</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -11244,7 +11244,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #140 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #140 Performance Benchmark</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -11284,7 +11284,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #141 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #141 Performance Benchmark</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -11324,7 +11324,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #142 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #142 Performance Benchmark</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -11364,7 +11364,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #143 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #143 Performance Benchmark</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -11404,7 +11404,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #144 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #144 Performance Benchmark</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -11444,7 +11444,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #145 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #145 Performance Benchmark</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -11484,7 +11484,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #146 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #146 Performance Benchmark</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -11524,7 +11524,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #147 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #147 Performance Benchmark</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -11564,7 +11564,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #148 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #148 Performance Benchmark</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -11604,7 +11604,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #149 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #149 Performance Benchmark</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -11644,7 +11644,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #150 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #150 Performance Benchmark</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -11684,7 +11684,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #151 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #151 Performance Benchmark</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -11724,7 +11724,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #152 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #152 Performance Benchmark</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -11764,7 +11764,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #153 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #153 Performance Benchmark</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -11804,7 +11804,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #154 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #154 Performance Benchmark</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -11844,7 +11844,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #155 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #155 Performance Benchmark</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -11884,7 +11884,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #156 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #156 Performance Benchmark</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -11924,7 +11924,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #157 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #157 Performance Benchmark</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -11964,7 +11964,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #158 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #158 Performance Benchmark</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -12004,7 +12004,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #159 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #159 Performance Benchmark</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -12044,7 +12044,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #160 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #160 Performance Benchmark</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -12084,7 +12084,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #161 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #161 Performance Benchmark</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -12124,7 +12124,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #162 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #162 Performance Benchmark</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -12164,7 +12164,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #163 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #163 Performance Benchmark</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -12204,7 +12204,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #164 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #164 Performance Benchmark</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -12244,7 +12244,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #165 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #165 Performance Benchmark</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -12284,7 +12284,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #166 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #166 Performance Benchmark</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -12324,7 +12324,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #167 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #167 Performance Benchmark</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -12364,7 +12364,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #168 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #168 Performance Benchmark</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -12404,7 +12404,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #169 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #169 Performance Benchmark</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -12444,7 +12444,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #170 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #170 Performance Benchmark</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -12484,7 +12484,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #171 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #171 Performance Benchmark</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -12524,7 +12524,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #172 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #172 Performance Benchmark</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -12564,7 +12564,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #173 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #173 Performance Benchmark</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -12604,7 +12604,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #174 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #174 Performance Benchmark</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -12644,7 +12644,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Backend API Microservice Scenario #175 Performance Benchmark</t>
+          <t>Infrastructure Component Scenario #175 Performance Benchmark</t>
         </is>
       </c>
       <c r="B306" t="n">
